--- a/DuePrint3 BOM.xlsx
+++ b/DuePrint3 BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jared\Documents\GitHub\DuePrint3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B548CD0-C516-41C1-8BDB-ACCF9EA7F69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F38D6A-2F9F-40BD-A021-923E75D44912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="27000" windowHeight="12855" xr2:uid="{EE4BCC0D-CA0F-44AB-9A6C-651FC0043629}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25800" windowHeight="21000" xr2:uid="{EE4BCC0D-CA0F-44AB-9A6C-651FC0043629}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="208">
   <si>
     <t>Item</t>
   </si>
@@ -578,9 +578,6 @@
     <t>Jumper, Shorting, 2 Pos</t>
   </si>
   <si>
-    <t>SPHD-002-P0.5</t>
-  </si>
-  <si>
     <t>0.1 uF, 100V X7R Cap, 0805</t>
   </si>
   <si>
@@ -624,6 +621,48 @@
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/samtec-inc/EHT-125-01-F-D/6694880</t>
+  </si>
+  <si>
+    <t>DuetScreen</t>
+  </si>
+  <si>
+    <t>https://www.filastruder.com/collections/electronics/products/duet3d-duetscreen</t>
+  </si>
+  <si>
+    <t>Duet 6HC &lt;-&gt; DuetScreen, cable needs to support data</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B08PVPTNZL?th=1</t>
+  </si>
+  <si>
+    <t>10ft USB-C Cable</t>
+  </si>
+  <si>
+    <t>SPHD-002T-P0.5</t>
+  </si>
+  <si>
+    <t>Interface Plate</t>
+  </si>
+  <si>
+    <t>48VDC Plate</t>
+  </si>
+  <si>
+    <t>Fan Bracket</t>
+  </si>
+  <si>
+    <t>MCU Module</t>
+  </si>
+  <si>
+    <t>https://github.com/jcwebber93/DP3EXB</t>
+  </si>
+  <si>
+    <t>https://github.com/jcwebber93/DuePrint3/blob/v2.5.0/Fan%20Bracket.STEP</t>
+  </si>
+  <si>
+    <t>https://github.com/jcwebber93/DuePrint3/blob/v2.5.0/Interface%20Plate.STEP</t>
+  </si>
+  <si>
+    <t>https://github.com/jcwebber93/DuePrint3/blob/v2.5.0/48VDC%20Plate.STEP</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5704B641-D666-4847-A317-F8C12FBC4158}">
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="5" bestFit="1" customWidth="1"/>
@@ -1109,7 +1148,7 @@
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F1" s="7">
         <f>SUM(G:G)</f>
-        <v>459.93657600000034</v>
+        <v>661.00657600000034</v>
       </c>
       <c r="H1" s="10" t="s">
         <v>105</v>
@@ -1245,7 +1284,7 @@
         <v>84</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -1273,7 +1312,7 @@
         <v>29</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D8" s="1">
         <v>2</v>
@@ -1382,7 +1421,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
@@ -1402,7 +1441,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1552,7 +1591,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>70</v>
@@ -1572,7 +1611,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1669,7 +1708,7 @@
         <v>31</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -1697,7 +1736,7 @@
         <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -1725,7 +1764,7 @@
         <v>82</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
@@ -1781,7 +1820,7 @@
         <v>32</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D26" s="1">
         <v>8</v>
@@ -1837,7 +1876,7 @@
         <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -1865,7 +1904,7 @@
         <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D29" s="1">
         <v>3</v>
@@ -1908,7 +1947,12 @@
         <f t="shared" si="10"/>
         <v>40</v>
       </c>
-      <c r="H30" s="1"/>
+      <c r="H30" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
@@ -2177,10 +2221,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D41" s="1">
         <v>27</v>
@@ -2193,7 +2237,7 @@
         <v>0.56700000000000006</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2581,7 +2625,7 @@
         <v>6.6055000000000001</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -2603,7 +2647,7 @@
         <v>5.7949999999999999</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -2625,7 +2669,7 @@
         <v>11.837076000000001</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -2636,7 +2680,7 @@
         <v>104</v>
       </c>
       <c r="D59" s="1">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F59" s="4">
         <f>8.85/25</f>
@@ -2644,52 +2688,141 @@
       </c>
       <c r="G59" s="4">
         <f>D59*F59</f>
-        <v>18.407999999999998</v>
+        <v>25.488</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
+        <v>58</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="4">
+        <v>123</v>
+      </c>
       <c r="G60" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
+        <v>59</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="4">
+        <v>9.99</v>
+      </c>
       <c r="G61" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9.99</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="5">
+        <v>60</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="4">
+        <v>30</v>
+      </c>
       <c r="G62" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
+        <v>61</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="4">
+        <v>15</v>
+      </c>
       <c r="G63" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
+        <v>62</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D64" s="1">
+        <v>2</v>
+      </c>
+      <c r="F64" s="4">
+        <v>8</v>
+      </c>
       <c r="G64" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="7:7" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
+        <v>63</v>
+      </c>
       <c r="G65" s="4">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
+        <v>64</v>
+      </c>
       <c r="G66" s="4">
         <f t="shared" si="11"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2741,6 +2874,12 @@
     <hyperlink ref="I29" r:id="rId44" xr:uid="{5BE81EE3-B855-4FB7-AFEB-EF4F933CF706}"/>
     <hyperlink ref="I31" r:id="rId45" xr:uid="{93EDBFF8-7106-49F8-92AE-32C5583BC207}"/>
     <hyperlink ref="I19" r:id="rId46" xr:uid="{69C62FD5-32F0-48B7-AED5-E7D2D1121B21}"/>
+    <hyperlink ref="I60" r:id="rId47" xr:uid="{8BA393C8-AD30-49A8-ABBC-D481919681FB}"/>
+    <hyperlink ref="I61" r:id="rId48" xr:uid="{975362B0-1B9E-460D-9F1E-EA7E349DAB9B}"/>
+    <hyperlink ref="I30" r:id="rId49" xr:uid="{F825E3FC-5FFC-4BAD-92B2-E436F474B91D}"/>
+    <hyperlink ref="I64" r:id="rId50" xr:uid="{E40D2601-7A71-481A-B8D1-CD25DE4CD59A}"/>
+    <hyperlink ref="I62" r:id="rId51" xr:uid="{C28DBDBF-7EBF-4389-AA4F-DDFE9D86616A}"/>
+    <hyperlink ref="I63" r:id="rId52" xr:uid="{98671E6B-4E5F-4705-B05C-9CD983E6717E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DuePrint3 BOM.xlsx
+++ b/DuePrint3 BOM.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F38D6A-2F9F-40BD-A021-923E75D44912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25800" windowHeight="21000" xr2:uid="{EE4BCC0D-CA0F-44AB-9A6C-651FC0043629}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{EE4BCC0D-CA0F-44AB-9A6C-651FC0043629}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
